--- a/dados/SURVEY_STARNAV_D1.xlsx
+++ b/dados/SURVEY_STARNAV_D1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_22B7D168C55302150E5C0D74A28AD5F518C06C90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98B2C7E5-D4D5-4D6D-ADD1-AB03185EF137}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_22B7D168C55302150E5C0D74A28AD5F518C06C90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D68E25FB-AD40-430C-B4C0-C5ABA69E14CA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="STARNAV ANDROMEDA" sheetId="1" r:id="rId1"/>
@@ -316,7 +316,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -373,7 +373,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2970,6 +2970,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
